--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_97_R10.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_97_R10.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>D. WASHINGTON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.366</v>
+        <v>2.116</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5581</v>
+        <v>1.3083</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8079</v>
+        <v>0.8076</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5967</v>
+        <v>2.9368</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1766</v>
+        <v>-1.2353</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7733</v>
+        <v>4.1722</v>
       </c>
       <c r="J2" t="n">
-        <v>1.436</v>
+        <v>2.4408</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07770000000000001</v>
+        <v>-0.423</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3583</v>
+        <v>2.8638</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1607</v>
+        <v>0.4961</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2543</v>
+        <v>-0.8123</v>
       </c>
       <c r="O2" t="n">
-        <v>0.415</v>
+        <v>1.3084</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3596</v>
+        <v>0.5012</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3541</v>
+        <v>0.0633</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0056</v>
+        <v>0.438</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.7501</v>
+        <v>-0.3943</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.3558</v>
       </c>
       <c r="X2" t="n">
         <v>-1.7501</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. WASHINGTON</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4181</v>
+        <v>1.8112</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2154</v>
+        <v>1.4401</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2027</v>
+        <v>0.371</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9368</v>
+        <v>1.5967</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2353</v>
+        <v>-0.1766</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1722</v>
+        <v>1.7733</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4408</v>
+        <v>1.436</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.423</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8638</v>
+        <v>1.3583</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4961</v>
+        <v>0.1607</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8123</v>
+        <v>-0.2543</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3084</v>
+        <v>0.415</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1967</v>
+        <v>0.8048</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0297</v>
+        <v>0.2361</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1669</v>
+        <v>0.5687</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3943</v>
+        <v>-1.7501</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3558</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>-1.7501</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.321</v>
+        <v>0.6145</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2819</v>
+        <v>-0.0893</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6029</v>
+        <v>0.7037</v>
       </c>
       <c r="G4" t="n">
         <v>0.4778</v>
@@ -766,13 +766,13 @@
         <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3888</v>
+        <v>-0.0953</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2987</v>
+        <v>-0.1061</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2662</v>
+        <v>0.3922</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4267</v>
+        <v>0.0018</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6929</v>
+        <v>0.3904</v>
       </c>
       <c r="G5" t="n">
         <v>1.6463</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.156</v>
+        <v>0.282</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7389</v>
+        <v>-0.3104</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8949</v>
+        <v>0.5924</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1934</v>
+        <v>-0.4451</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7826</v>
+        <v>-1.6646</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5892</v>
+        <v>1.2195</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2996</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6576</v>
+        <v>0.4059</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2513</v>
+        <v>-0.1333</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9089</v>
+        <v>0.5392</v>
       </c>
       <c r="V6" t="n">
         <v>1.0722</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>N. CALATHES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5997</v>
+        <v>-0.7257</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9937</v>
+        <v>-2.918</v>
       </c>
       <c r="F7" t="n">
-        <v>0.394</v>
+        <v>2.1923</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1369</v>
+        <v>-1.1717</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5485</v>
+        <v>-2.1453</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4116</v>
+        <v>0.9736</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3318</v>
+        <v>-0.9644</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0742</v>
+        <v>-1.7338</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2576</v>
+        <v>0.7694</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4687</v>
+        <v>-0.2073</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6227</v>
+        <v>-0.4116</v>
       </c>
       <c r="O7" t="n">
-        <v>0.154</v>
+        <v>0.2042</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.7834</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.9432</v>
+        <v>-1.6237</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6042</v>
+        <v>0.3558</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5454</v>
+        <v>-0.3299</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0587</v>
+        <v>0.6858</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3558</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.8774</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0735</v>
+        <v>-0.3527</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7264</v>
+        <v>-0.5248</v>
       </c>
       <c r="G8" t="n">
         <v>0.792</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3901</v>
+        <v>0.3126</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0351</v>
+        <v>-0.3143</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4252</v>
+        <v>0.6269</v>
       </c>
       <c r="V8" t="n">
         <v>-1.7501</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. CALATHES</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8408</v>
+        <v>-0.905</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8314</v>
+        <v>-1.1536</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9906</v>
+        <v>0.2487</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1717</v>
+        <v>3.0018</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1453</v>
+        <v>0.1646</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9736</v>
+        <v>2.8372</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9644</v>
+        <v>2.4195</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7338</v>
+        <v>0.1043</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7694</v>
+        <v>2.3152</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2073</v>
+        <v>0.5823</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4116</v>
+        <v>0.0602</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2042</v>
+        <v>0.5221</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.6237</v>
+        <v>-3.9432</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2407</v>
+        <v>0.4127</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2434</v>
+        <v>0.2282</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4841</v>
+        <v>0.1845</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9214</v>
+        <v>-1.9734</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0357</v>
+        <v>-2.0985</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1143</v>
+        <v>0.1251</v>
       </c>
       <c r="G10" t="n">
-        <v>3.0018</v>
+        <v>-0.1369</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1646</v>
+        <v>-0.5485</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8372</v>
+        <v>0.4116</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4195</v>
+        <v>0.3318</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1043</v>
+        <v>0.0742</v>
       </c>
       <c r="L10" t="n">
-        <v>2.3152</v>
+        <v>0.2576</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5823</v>
+        <v>-0.4687</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0602</v>
+        <v>-0.6227</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5221</v>
+        <v>0.154</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.2473</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q10" t="n">
         <v>-3.9432</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3962</v>
+        <v>1.2305</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3462</v>
+        <v>0.4406</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0501</v>
+        <v>0.7899</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.214</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3704</v>
+        <v>-2.6148</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.624</v>
+        <v>-3.0028</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2536</v>
+        <v>0.388</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2543</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7398</v>
+        <v>0.0158</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1202</v>
+        <v>-0.4991</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3804</v>
+        <v>0.5149</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3543</v>
+        <v>-2.6075</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.276000000000002</v>
+        <v>-8.529300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>5.9217</v>
+        <v>5.9215</v>
       </c>
       <c r="G12" t="n">
         <v>6.588899999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.1328</v>
+        <v>-8.132800000000001</v>
       </c>
       <c r="I12" t="n">
         <v>14.7219</v>
@@ -1381,7 +1381,7 @@
         <v>4.1665</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.9584</v>
+        <v>-6.958400000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-18.5564</v>
@@ -1390,16 +1390,16 @@
         <v>11.5978</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4791</v>
+        <v>4.226</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4716</v>
+        <v>-0.7249000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>4.9509</v>
+        <v>4.9511</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.464300000000001</v>
+        <v>-6.4643</v>
       </c>
       <c r="W12" t="n">
         <v>5.7864</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.774</v>
+        <v>6.015</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8408</v>
+        <v>3.7228</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9333</v>
+        <v>2.2922</v>
       </c>
       <c r="G13" t="n">
         <v>4.2321</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.1592</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4129</v>
+        <v>0.295</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4946</v>
+        <v>-0.1357</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4996</v>
+        <v>3.2349</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8582</v>
+        <v>-0.056</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6415</v>
+        <v>3.2909</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0744</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2182</v>
+        <v>1.4275</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1438</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5808</v>
+        <v>-0.7197</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3501</v>
+        <v>-0.0805</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2308</v>
+        <v>-0.6391</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4936</v>
+        <v>1.5015</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8681</v>
+        <v>1.508</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3746</v>
+        <v>-0.0065</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.0876</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>1.353</v>
+        <v>0.3655</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4525</v>
+        <v>-0.4086</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9006</v>
+        <v>0.7741</v>
       </c>
       <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.0722</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.1444</v>
       </c>
       <c r="X14" t="n">
         <v>-1.0722</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4809</v>
+        <v>3.0367</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.056</v>
+        <v>-0.1136</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5369</v>
+        <v>3.1502</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7818000000000001</v>
+        <v>2.1462</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4275</v>
+        <v>1.2629</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6457000000000001</v>
+        <v>0.8833</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7197</v>
+        <v>1.156</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0805</v>
+        <v>0.3732</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6391</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5015</v>
+        <v>0.9902</v>
       </c>
       <c r="N15" t="n">
-        <v>1.508</v>
+        <v>0.8897</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0065</v>
+        <v>0.1005</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6115</v>
+        <v>0.1946</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4086</v>
+        <v>-0.1098</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0201</v>
+        <v>0.3044</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8122</v>
+        <v>2.7539</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1136</v>
+        <v>0.2684</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9258</v>
+        <v>2.4855</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1462</v>
+        <v>1.0744</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2629</v>
+        <v>1.2182</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8833</v>
+        <v>-0.1438</v>
       </c>
       <c r="J16" t="n">
-        <v>1.156</v>
+        <v>0.5808</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3732</v>
+        <v>0.3501</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.2308</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9902</v>
+        <v>0.4936</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8897</v>
+        <v>0.8681</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1005</v>
+        <v>-0.3746</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0299</v>
+        <v>0.6073</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1098</v>
+        <v>-0.1373</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08</v>
+        <v>0.7446</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4031</v>
+        <v>0.7963</v>
       </c>
       <c r="E17" t="n">
-        <v>1.757</v>
+        <v>1.9929</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3539</v>
+        <v>-1.1967</v>
       </c>
       <c r="G17" t="n">
         <v>0.019</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0772</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1949</v>
+        <v>-0.959</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1177</v>
+        <v>0.275</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3943</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0779</v>
+        <v>0.6635</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3915</v>
+        <v>-0.9466</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3136</v>
+        <v>1.6101</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9213</v>
+        <v>-3.4873</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8536</v>
+        <v>-0.4024</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0677</v>
+        <v>-3.085</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4268</v>
+        <v>-2.5834</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4636</v>
+        <v>-0.9236</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0368</v>
+        <v>-1.6597</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4945</v>
+        <v>-0.9039</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.39</v>
+        <v>0.5213</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1045</v>
+        <v>-1.4252</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>3.2473</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8395</v>
+        <v>-0.6172</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6765</v>
+        <v>-0.5619</v>
       </c>
       <c r="U18" t="n">
-        <v>0.163</v>
+        <v>-0.0553</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5361</v>
+        <v>2.6805</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1418</v>
+        <v>3.3584</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3943</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3359</v>
+        <v>-0.8764</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6543</v>
+        <v>-0.5521</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3184</v>
+        <v>-0.3244</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.4873</v>
+        <v>-2.9213</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4024</v>
+        <v>-0.8536</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.085</v>
+        <v>-2.0677</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.5834</v>
+        <v>-0.4268</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9236</v>
+        <v>-0.4636</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.6597</v>
+        <v>0.0368</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9039</v>
+        <v>-2.4945</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5213</v>
+        <v>-0.39</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4252</v>
+        <v>-2.1045</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.2473</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6166</v>
+        <v>-0.1149</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2696</v>
+        <v>-0.2671</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.347</v>
+        <v>0.1522</v>
       </c>
       <c r="V19" t="n">
-        <v>2.6805</v>
+        <v>0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>3.3584</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7282</v>
+        <v>-2.4251</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6543</v>
+        <v>-2.4184</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0738</v>
+        <v>-0.0066</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1522</v>
@@ -2014,13 +2014,13 @@
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9498</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9709</v>
+        <v>-0.735</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0211</v>
+        <v>0.0883</v>
       </c>
       <c r="V20" t="n">
         <v>0.1418</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6304</v>
+        <v>-2.716</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6811</v>
+        <v>-2.3273</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9493</v>
+        <v>-0.3888</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1579</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4725</v>
+        <v>-0.5581</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4189</v>
+        <v>-1.0651</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0536</v>
+        <v>0.507</v>
       </c>
       <c r="V21" t="n">
         <v>0.5361</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9988</v>
+        <v>-5.5555</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.8237</v>
+        <v>-6.7057</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8249</v>
+        <v>1.1502</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1238</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0556</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1202</v>
+        <v>-1.0023</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0646</v>
+        <v>0.3899</v>
       </c>
       <c r="V22" t="n">
         <v>1.8919</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.354400000000001</v>
+        <v>4.927300000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.1355</v>
+        <v>-7.135600000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>10.4902</v>
+        <v>12.0626</v>
       </c>
       <c r="G23" t="n">
         <v>-6.589</v>
@@ -2233,7 +2233,7 @@
         <v>-4.965300000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>5.59</v>
+        <v>5.590000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>-10.5553</v>
@@ -2248,16 +2248,16 @@
         <v>18.5562</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.479299999999999</v>
+        <v>-1.9067</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.951000000000001</v>
+        <v>-4.951099999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4719</v>
+        <v>3.0445</v>
       </c>
       <c r="V23" t="n">
-        <v>6.4643</v>
+        <v>6.464300000000001</v>
       </c>
       <c r="W23" t="n">
         <v>11.0367</v>
